--- a/outputs/79-7.xlsx
+++ b/outputs/79-7.xlsx
@@ -694,11 +694,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
